--- a/templates/fellowship-database-template.xlsx
+++ b/templates/fellowship-database-template.xlsx
@@ -322,7 +322,7 @@
     </comment>
     <comment ref="T1" authorId="0" shapeId="0">
       <text>
-        <t>Where the fellowship must be held. Blank = anywhere.</t>
+        <t>Where it must be held: two-letter codes, e.g. US, or any if it can be held anywhere. Blank means not stated, shown to users as worth checking.</t>
       </text>
     </comment>
     <comment ref="U1" authorId="0" shapeId="0">
@@ -879,7 +879,7 @@
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Countries: two-letter codes separated by commas, e.g. IN, DE, GB, US. Blank means no restriction.</t>
+          <t>Countries: two-letter codes separated by commas, e.g. IN, DE, GB, US. For host_countries, write any if it can be held anywhere; blank means not stated, which Galley shows as worth checking. For the other country columns, blank means no restriction.</t>
         </is>
       </c>
     </row>
@@ -942,6 +942,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
